--- a/assets/rutinas-hombre-doble-progresion.xlsx
+++ b/assets/rutinas-hombre-doble-progresion.xlsx
@@ -2880,7 +2880,7 @@
     <row r="999" ht="15.75" customHeight="1" s="86"/>
     <row r="1000" ht="15.75" customHeight="1" s="86"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="851A"/>
   <mergeCells count="15">
     <mergeCell ref="B22:K22"/>
     <mergeCell ref="B1:K1"/>

--- a/assets/rutinas-hombre-doble-progresion.xlsx
+++ b/assets/rutinas-hombre-doble-progresion.xlsx
@@ -9262,7 +9262,7 @@
     <row r="999" ht="15.75" customHeight="1" s="86"/>
     <row r="1000" ht="15.75" customHeight="1" s="86"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="de97"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="851A"/>
   <autoFilter ref="B4:F68"/>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
@@ -21312,7 +21312,7 @@
     <row r="999" ht="15.75" customHeight="1" s="86"/>
     <row r="1000" ht="15.75" customHeight="1" s="86"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="de97"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="851A"/>
   <mergeCells count="52">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="E24:F24"/>
@@ -36857,7 +36857,7 @@
     <row r="530" ht="15.75" customHeight="1" s="86"/>
     <row r="531" ht="15.75" customHeight="1" s="86"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="de97"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="851A"/>
   <mergeCells count="60">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="E24:F24"/>
@@ -54052,7 +54052,7 @@
     <row r="569" ht="15.75" customHeight="1" s="86"/>
     <row r="570" ht="15.75" customHeight="1" s="86"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="de97"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="851A"/>
   <mergeCells count="64">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="E24:F24"/>
@@ -73439,7 +73439,7 @@
     <row r="621" ht="15.75" customHeight="1" s="86"/>
     <row r="622" ht="15.75" customHeight="1" s="86"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="de97"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="851A"/>
   <mergeCells count="69">
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="B7:F7"/>
